--- a/data/db/subsystem_document.xlsx
+++ b/data/db/subsystem_document.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1168"/>
+  <dimension ref="A1:C1243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20273,6 +20273,1281 @@
         </is>
       </c>
     </row>
+    <row r="1169">
+      <c r="A1169" s="1" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="B1169" s="1" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="C1169" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" s="1" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="B1170" s="1" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="C1170" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="1" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="B1171" s="1" t="inlineStr">
+        <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="C1171" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="1" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="B1172" s="1" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="C1172" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="1" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="B1173" s="1" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="C1173" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="1" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="B1174" s="1" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="C1174" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="1" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="B1175" s="1" t="inlineStr">
+        <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="C1175" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="1" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="B1176" s="1" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="C1176" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="1" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="B1177" s="1" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="C1177" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="1" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="B1178" s="1" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="C1178" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="1" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="B1179" s="1" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="C1179" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="1" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="B1180" s="1" t="inlineStr">
+        <is>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="C1180" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="1" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="B1181" s="1" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C1181" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="1" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="B1182" s="1" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C1182" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="1" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="B1183" s="1" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="C1183" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="1" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="B1184" s="1" t="inlineStr">
+        <is>
+          <t>952</t>
+        </is>
+      </c>
+      <c r="C1184" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="1" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="B1185" s="1" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="C1185" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="1" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="B1186" s="1" t="inlineStr">
+        <is>
+          <t>954</t>
+        </is>
+      </c>
+      <c r="C1186" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="1" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="B1187" s="1" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="C1187" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="1" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="B1188" s="1" t="inlineStr">
+        <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="C1188" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="1" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="B1189" s="1" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="C1189" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="1" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="B1190" s="1" t="inlineStr">
+        <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="C1190" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="1" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="B1191" s="1" t="inlineStr">
+        <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="C1191" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="1" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="B1192" s="1" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="C1192" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="1" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="B1193" s="1" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="C1193" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" s="1" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="B1194" s="1" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="C1194" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" s="1" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="B1195" s="1" t="inlineStr">
+        <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="C1195" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" s="1" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="B1196" s="1" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="C1196" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" s="1" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="B1197" s="1" t="inlineStr">
+        <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="C1197" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" s="1" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="B1198" s="1" t="inlineStr">
+        <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="C1198" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" s="1" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="B1199" s="1" t="inlineStr">
+        <is>
+          <t>967</t>
+        </is>
+      </c>
+      <c r="C1199" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" s="1" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="B1200" s="1" t="inlineStr">
+        <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="C1200" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" s="1" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="B1201" s="1" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="C1201" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" s="1" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="B1202" s="1" t="inlineStr">
+        <is>
+          <t>970</t>
+        </is>
+      </c>
+      <c r="C1202" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" s="1" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="B1203" s="1" t="inlineStr">
+        <is>
+          <t>971</t>
+        </is>
+      </c>
+      <c r="C1203" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" s="1" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="B1204" s="1" t="inlineStr">
+        <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="C1204" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" s="1" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="B1205" s="1" t="inlineStr">
+        <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="C1205" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" s="1" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="B1206" s="1" t="inlineStr">
+        <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="C1206" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" s="1" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="B1207" s="1" t="inlineStr">
+        <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="C1207" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" s="1" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="B1208" s="1" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="C1208" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" s="1" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="B1209" s="1" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="C1209" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" s="1" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="B1210" s="1" t="inlineStr">
+        <is>
+          <t>978</t>
+        </is>
+      </c>
+      <c r="C1210" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" s="1" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="B1211" s="1" t="inlineStr">
+        <is>
+          <t>979</t>
+        </is>
+      </c>
+      <c r="C1211" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" s="1" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="B1212" s="1" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="C1212" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" s="1" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="B1213" s="1" t="inlineStr">
+        <is>
+          <t>981</t>
+        </is>
+      </c>
+      <c r="C1213" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" s="1" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="B1214" s="1" t="inlineStr">
+        <is>
+          <t>982</t>
+        </is>
+      </c>
+      <c r="C1214" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" s="1" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="B1215" s="1" t="inlineStr">
+        <is>
+          <t>983</t>
+        </is>
+      </c>
+      <c r="C1215" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" s="1" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="B1216" s="1" t="inlineStr">
+        <is>
+          <t>984</t>
+        </is>
+      </c>
+      <c r="C1216" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" s="1" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="B1217" s="1" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="C1217" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="1" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="B1218" s="1" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="C1218" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" s="1" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="B1219" s="1" t="inlineStr">
+        <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="C1219" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" s="1" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="B1220" s="1" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="C1220" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" s="1" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="B1221" s="1" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="C1221" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" s="1" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="B1222" s="1" t="inlineStr">
+        <is>
+          <t>989</t>
+        </is>
+      </c>
+      <c r="C1222" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" s="1" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="B1223" s="1" t="inlineStr">
+        <is>
+          <t>990</t>
+        </is>
+      </c>
+      <c r="C1223" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" s="1" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="B1224" s="1" t="inlineStr">
+        <is>
+          <t>989</t>
+        </is>
+      </c>
+      <c r="C1224" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" s="1" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="B1225" s="1" t="inlineStr">
+        <is>
+          <t>991</t>
+        </is>
+      </c>
+      <c r="C1225" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" s="1" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="B1226" s="1" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="C1226" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" s="1" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="B1227" s="1" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="C1227" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" s="1" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="B1228" s="1" t="inlineStr">
+        <is>
+          <t>994</t>
+        </is>
+      </c>
+      <c r="C1228" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" s="1" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="B1229" s="1" t="inlineStr">
+        <is>
+          <t>995</t>
+        </is>
+      </c>
+      <c r="C1229" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" s="1" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="B1230" s="1" t="inlineStr">
+        <is>
+          <t>996</t>
+        </is>
+      </c>
+      <c r="C1230" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" s="1" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="B1231" s="1" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="C1231" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" s="1" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="B1232" s="1" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="C1232" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" s="1" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="B1233" s="1" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="C1233" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" s="1" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="B1234" s="1" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="C1234" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" s="1" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="B1235" s="1" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="C1235" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" s="1" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="B1236" s="1" t="inlineStr">
+        <is>
+          <t>1002</t>
+        </is>
+      </c>
+      <c r="C1236" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" s="1" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="B1237" s="1" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="C1237" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" s="1" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="B1238" s="1" t="inlineStr">
+        <is>
+          <t>989</t>
+        </is>
+      </c>
+      <c r="C1238" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" s="1" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="B1239" s="1" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="C1239" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" s="1" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="B1240" s="1" t="inlineStr">
+        <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="C1240" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" s="1" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="B1241" s="1" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="C1241" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" s="1" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="B1242" s="1" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="C1242" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" s="1" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="B1243" s="1" t="inlineStr">
+        <is>
+          <t>1008</t>
+        </is>
+      </c>
+      <c r="C1243" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/db/subsystem_document.xlsx
+++ b/data/db/subsystem_document.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1243"/>
+  <dimension ref="A1:C1268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21548,6 +21548,431 @@
         </is>
       </c>
     </row>
+    <row r="1244">
+      <c r="A1244" s="1" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="B1244" s="1" t="inlineStr">
+        <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="C1244" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" s="1" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="B1245" s="1" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="C1245" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" s="1" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="B1246" s="1" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="C1246" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" s="1" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="B1247" s="1" t="inlineStr">
+        <is>
+          <t>1012</t>
+        </is>
+      </c>
+      <c r="C1247" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" s="1" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="B1248" s="1" t="inlineStr">
+        <is>
+          <t>1013</t>
+        </is>
+      </c>
+      <c r="C1248" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" s="1" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="B1249" s="1" t="inlineStr">
+        <is>
+          <t>1014</t>
+        </is>
+      </c>
+      <c r="C1249" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" s="1" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="B1250" s="1" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C1250" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" s="1" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="B1251" s="1" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="C1251" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" s="1" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="B1252" s="1" t="inlineStr">
+        <is>
+          <t>1017</t>
+        </is>
+      </c>
+      <c r="C1252" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" s="1" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="B1253" s="1" t="inlineStr">
+        <is>
+          <t>1018</t>
+        </is>
+      </c>
+      <c r="C1253" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" s="1" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="B1254" s="1" t="inlineStr">
+        <is>
+          <t>1019</t>
+        </is>
+      </c>
+      <c r="C1254" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" s="1" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="B1255" s="1" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="C1255" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" s="1" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="B1256" s="1" t="inlineStr">
+        <is>
+          <t>1021</t>
+        </is>
+      </c>
+      <c r="C1256" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" s="1" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="B1257" s="1" t="inlineStr">
+        <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="C1257" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" s="1" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="B1258" s="1" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C1258" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" s="1" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="B1259" s="1" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="C1259" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" s="1" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="B1260" s="1" t="inlineStr">
+        <is>
+          <t>1025</t>
+        </is>
+      </c>
+      <c r="C1260" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" s="1" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="B1261" s="1" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="C1261" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" s="1" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="B1262" s="1" t="inlineStr">
+        <is>
+          <t>1027</t>
+        </is>
+      </c>
+      <c r="C1262" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" s="1" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="B1263" s="1" t="inlineStr">
+        <is>
+          <t>1028</t>
+        </is>
+      </c>
+      <c r="C1263" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" s="1" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="B1264" s="1" t="inlineStr">
+        <is>
+          <t>1029</t>
+        </is>
+      </c>
+      <c r="C1264" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" s="1" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="B1265" s="1" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="C1265" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="1" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="B1266" s="1" t="inlineStr">
+        <is>
+          <t>1031</t>
+        </is>
+      </c>
+      <c r="C1266" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="1" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="B1267" s="1" t="inlineStr">
+        <is>
+          <t>1032</t>
+        </is>
+      </c>
+      <c r="C1267" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="1" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="B1268" s="1" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="C1268" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
